--- a/database/persona-db.xlsx
+++ b/database/persona-db.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cableoneinc-my.sharepoint.com/personal/farrellt_corp_cableone_net/Documents/Desktop/Persona_Site/Official/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cableoneinc-my.sharepoint.com/personal/farrellt_corp_cableone_net/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A972C3A3-7595-4CE7-BAA2-233AA1D50605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{A972C3A3-7595-4CE7-BAA2-233AA1D50605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6ED9D21-6A6E-4125-8990-3A1AB872EA6C}"/>
   <bookViews>
-    <workbookView xWindow="15630" yWindow="945" windowWidth="51840" windowHeight="21120" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15630" yWindow="945" windowWidth="51840" windowHeight="21120" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
     <sheet name="12_DataHealth" sheetId="14" r:id="rId14"/>
     <sheet name="99_Glossary" sheetId="15" r:id="rId15"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'07_PricingSchedules'!$A$1:$I$175</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="510">
   <si>
     <t>Persona Offer Database v6</t>
   </si>
@@ -1162,9 +1165,6 @@
   </si>
   <si>
     <t>Months 36 Months</t>
-  </si>
-  <si>
-    <t>Months with AutoPay, Paperless Billing</t>
   </si>
   <si>
     <t>Title</t>
@@ -1900,10 +1900,10 @@
         <v>111</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>39</v>
@@ -1914,10 +1914,10 @@
         <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>43</v>
@@ -1928,10 +1928,10 @@
         <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>43</v>
@@ -1942,10 +1942,10 @@
         <v>123</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>43</v>
@@ -1956,10 +1956,10 @@
         <v>126</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>43</v>
@@ -1970,10 +1970,10 @@
         <v>129</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>43</v>
@@ -1984,10 +1984,10 @@
         <v>132</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>43</v>
@@ -1998,10 +1998,10 @@
         <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>43</v>
@@ -2012,10 +2012,10 @@
         <v>138</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>43</v>
@@ -2026,10 +2026,10 @@
         <v>141</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>43</v>
@@ -2040,10 +2040,10 @@
         <v>144</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>43</v>
@@ -2054,10 +2054,10 @@
         <v>147</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>43</v>
@@ -2068,10 +2068,10 @@
         <v>150</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>43</v>
@@ -2082,10 +2082,10 @@
         <v>153</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>404</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>43</v>
@@ -2096,10 +2096,10 @@
         <v>156</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2110,10 +2110,10 @@
         <v>159</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -2124,10 +2124,10 @@
         <v>162</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>43</v>
@@ -2138,10 +2138,10 @@
         <v>165</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>43</v>
@@ -2152,10 +2152,10 @@
         <v>168</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>414</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>43</v>
@@ -2166,10 +2166,10 @@
         <v>171</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>43</v>
@@ -2180,10 +2180,10 @@
         <v>174</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>43</v>
@@ -2194,10 +2194,10 @@
         <v>177</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>43</v>
@@ -2208,10 +2208,10 @@
         <v>180</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>422</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>43</v>
@@ -2222,10 +2222,10 @@
         <v>183</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>43</v>
@@ -2236,10 +2236,10 @@
         <v>186</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>43</v>
@@ -2250,10 +2250,10 @@
         <v>189</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>43</v>
@@ -2264,10 +2264,10 @@
         <v>192</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>43</v>
@@ -2278,10 +2278,10 @@
         <v>195</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>43</v>
@@ -2292,10 +2292,10 @@
         <v>198</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>434</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>43</v>
@@ -2306,10 +2306,10 @@
         <v>201</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>43</v>
@@ -2320,10 +2320,10 @@
         <v>204</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>43</v>
@@ -2348,13 +2348,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15">
       <c r="A1" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>85</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>75</v>
@@ -2374,13 +2374,13 @@
         <v>76</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>78</v>
@@ -2389,13 +2389,13 @@
         <v>79</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>88</v>
@@ -2404,13 +2404,13 @@
         <v>90</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>95</v>
@@ -2419,13 +2419,13 @@
         <v>82</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>98</v>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>103</v>
@@ -2475,7 +2475,7 @@
         <v>83</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>39</v>
@@ -3216,28 +3216,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15">
       <c r="A1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3259,19 +3259,19 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15">
       <c r="A1" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>460</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>107</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>461</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>462</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -3280,98 +3280,98 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="D2" s="3">
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D3">
         <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D4">
         <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D6">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
+        <v>474</v>
+      </c>
+      <c r="B7" t="s">
         <v>475</v>
       </c>
-      <c r="B7" t="s">
-        <v>476</v>
-      </c>
       <c r="C7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3379,13 +3379,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" t="s">
         <v>477</v>
       </c>
-      <c r="B8" t="s">
-        <v>478</v>
-      </c>
       <c r="C8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3393,13 +3393,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3407,13 +3407,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3421,13 +3421,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3435,13 +3435,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3449,13 +3449,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B13" t="s">
         <v>483</v>
       </c>
-      <c r="B13" t="s">
-        <v>484</v>
-      </c>
       <c r="C13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -3463,30 +3463,30 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
+        <v>486</v>
+      </c>
+      <c r="B15" t="s">
         <v>487</v>
       </c>
-      <c r="B15" t="s">
-        <v>488</v>
-      </c>
       <c r="C15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -3494,24 +3494,24 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B16" t="s">
         <v>489</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>490</v>
-      </c>
-      <c r="C16" t="s">
-        <v>491</v>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B18" t="s">
         <v>205</v>
@@ -3865,74 +3865,74 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3940,7 +3940,7 @@
         <v>368</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -5736,7 +5736,7 @@
   <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="40.25" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
@@ -8494,7 +8494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="28.5">
+    <row r="68" spans="1:13">
       <c r="A68" s="3" t="s">
         <v>336</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="28.5">
+    <row r="69" spans="1:13">
       <c r="A69" s="3" t="s">
         <v>338</v>
       </c>
@@ -9526,6 +9526,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I175"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -9540,7 +9543,7 @@
     <col min="9" max="9" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="5" t="s">
         <v>214</v>
       </c>
@@ -13279,7 +13282,7 @@
       </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:9" ht="28.5">
+    <row r="138" spans="1:9">
       <c r="A138" s="3" t="s">
         <v>337</v>
       </c>
@@ -13306,7 +13309,7 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" ht="28.5">
+    <row r="139" spans="1:9">
       <c r="A139" s="3" t="s">
         <v>339</v>
       </c>
@@ -13333,7 +13336,7 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" ht="28.5">
+    <row r="140" spans="1:9">
       <c r="A140" s="3" t="s">
         <v>339</v>
       </c>
@@ -13360,7 +13363,7 @@
       </c>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:9" ht="28.5">
+    <row r="141" spans="1:9">
       <c r="A141" s="3" t="s">
         <v>339</v>
       </c>
@@ -14278,7 +14281,7 @@
       </c>
       <c r="I174" s="3"/>
     </row>
-    <row r="175" spans="1:9" ht="28.5">
+    <row r="175" spans="1:9">
       <c r="A175" s="3" t="s">
         <v>362</v>
       </c>
@@ -14288,10 +14291,14 @@
       <c r="C175" s="3">
         <v>1</v>
       </c>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
+      <c r="D175" s="3">
+        <v>1</v>
+      </c>
+      <c r="E175" s="3">
+        <v>36</v>
+      </c>
       <c r="F175" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G175" s="3">
         <v>60</v>
@@ -14303,5 +14310,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="43" fitToHeight="4" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>